--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/83.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/83.xlsx
@@ -426,13 +426,13 @@
         <v>-8.611955370327541</v>
       </c>
       <c r="E2">
-        <v>-16.76131537688202</v>
+        <v>-15.24861033393779</v>
       </c>
       <c r="F2">
-        <v>-1.192167460906292</v>
+        <v>-0.477441296994642</v>
       </c>
       <c r="G2">
-        <v>-16.95592184352488</v>
+        <v>-14.09473816884497</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.241056236628566</v>
       </c>
       <c r="E3">
-        <v>-18.76205406363288</v>
+        <v>-16.44526411893869</v>
       </c>
       <c r="F3">
-        <v>-1.123899218139376</v>
+        <v>-0.3717043398642991</v>
       </c>
       <c r="G3">
-        <v>-15.93895039349785</v>
+        <v>-13.39187624540231</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.739528628378245</v>
       </c>
       <c r="E4">
-        <v>-18.14729107472159</v>
+        <v>-17.43734861911709</v>
       </c>
       <c r="F4">
-        <v>-0.8632376758678586</v>
+        <v>-0.3694925988988244</v>
       </c>
       <c r="G4">
-        <v>-15.85873587508131</v>
+        <v>-14.21584123521705</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.256101213926444</v>
       </c>
       <c r="E5">
-        <v>-18.84191823123216</v>
+        <v>-18.15757523919301</v>
       </c>
       <c r="F5">
-        <v>-0.9307529326656294</v>
+        <v>-0.3648056961337848</v>
       </c>
       <c r="G5">
-        <v>-14.77211882327187</v>
+        <v>-13.36428946942356</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.790193802376639</v>
       </c>
       <c r="E6">
-        <v>-18.92760148793129</v>
+        <v>-18.47998900311712</v>
       </c>
       <c r="F6">
-        <v>-1.158742007835929</v>
+        <v>-0.617297050711491</v>
       </c>
       <c r="G6">
-        <v>-14.19219400843004</v>
+        <v>-13.02891465356769</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.386586070067801</v>
       </c>
       <c r="E7">
-        <v>-20.16784183525601</v>
+        <v>-19.94523563846096</v>
       </c>
       <c r="F7">
-        <v>-0.8174065925731703</v>
+        <v>-0.4957614704749559</v>
       </c>
       <c r="G7">
-        <v>-13.33985764334374</v>
+        <v>-12.43758500934307</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.06234612284084951</v>
       </c>
       <c r="E8">
-        <v>-20.46693395804062</v>
+        <v>-20.36274735654615</v>
       </c>
       <c r="F8">
-        <v>-0.4880187203609889</v>
+        <v>-0.2638956358595547</v>
       </c>
       <c r="G8">
-        <v>-12.88113521124017</v>
+        <v>-11.69379150085286</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>1.134610165853239</v>
       </c>
       <c r="E9">
-        <v>-21.04697260826109</v>
+        <v>-20.74225612075896</v>
       </c>
       <c r="F9">
-        <v>-1.098389643970165</v>
+        <v>-0.2635791995116852</v>
       </c>
       <c r="G9">
-        <v>-12.58614242987233</v>
+        <v>-11.67679516005424</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>2.184351979789902</v>
       </c>
       <c r="E10">
-        <v>-22.27795222624013</v>
+        <v>-20.53807175622711</v>
       </c>
       <c r="F10">
-        <v>-0.8298039391234677</v>
+        <v>-0.2870319374197449</v>
       </c>
       <c r="G10">
-        <v>-12.57072852984148</v>
+        <v>-10.56418701521598</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.046629469562442</v>
       </c>
       <c r="E11">
-        <v>-22.96330053950898</v>
+        <v>-21.58400434083072</v>
       </c>
       <c r="F11">
-        <v>-0.4030978076955948</v>
+        <v>-0.3081329402712567</v>
       </c>
       <c r="G11">
-        <v>-10.99749438921457</v>
+        <v>-10.45731598411723</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.695616844521583</v>
       </c>
       <c r="E12">
-        <v>-24.27390431596489</v>
+        <v>-22.54686659823762</v>
       </c>
       <c r="F12">
-        <v>-0.1294814276116957</v>
+        <v>-0.0191975618073863</v>
       </c>
       <c r="G12">
-        <v>-10.84733797518984</v>
+        <v>-10.30312401508013</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>4.120312556932477</v>
       </c>
       <c r="E13">
-        <v>-23.57984774717929</v>
+        <v>-24.07899426620075</v>
       </c>
       <c r="F13">
-        <v>-0.2881966219880809</v>
+        <v>0.1710767738808545</v>
       </c>
       <c r="G13">
-        <v>-10.46866784477139</v>
+        <v>-8.636181572418609</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>4.312121762736743</v>
       </c>
       <c r="E14">
-        <v>-24.6531187293672</v>
+        <v>-23.71567479656536</v>
       </c>
       <c r="F14">
-        <v>0.1439825328700883</v>
+        <v>0.2911130091183225</v>
       </c>
       <c r="G14">
-        <v>-10.17993199447277</v>
+        <v>-8.683012549617139</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.292010033295857</v>
       </c>
       <c r="E15">
-        <v>-26.72352346025207</v>
+        <v>-24.34206690672834</v>
       </c>
       <c r="F15">
-        <v>0.2279781591465554</v>
+        <v>0.5277369860954041</v>
       </c>
       <c r="G15">
-        <v>-9.259646682192933</v>
+        <v>-8.51262208125639</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.094838479314676</v>
       </c>
       <c r="E16">
-        <v>-25.72665689152157</v>
+        <v>-24.99074363748307</v>
       </c>
       <c r="F16">
-        <v>0.1212537880720755</v>
+        <v>0.8199899760074865</v>
       </c>
       <c r="G16">
-        <v>-9.129734254140853</v>
+        <v>-7.321904924964564</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.765564259100736</v>
       </c>
       <c r="E17">
-        <v>-27.80349205549733</v>
+        <v>-25.68773012895164</v>
       </c>
       <c r="F17">
-        <v>0.5628291143801996</v>
+        <v>0.8356328660419523</v>
       </c>
       <c r="G17">
-        <v>-7.819188591509568</v>
+        <v>-7.520507862410983</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.358707774861191</v>
       </c>
       <c r="E18">
-        <v>-27.40193867981517</v>
+        <v>-27.79453926238416</v>
       </c>
       <c r="F18">
-        <v>0.6623541443569489</v>
+        <v>1.375042524457712</v>
       </c>
       <c r="G18">
-        <v>-7.701922447417505</v>
+        <v>-7.055283518868281</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.924170456328802</v>
       </c>
       <c r="E19">
-        <v>-28.69644373117381</v>
+        <v>-28.01798775534464</v>
       </c>
       <c r="F19">
-        <v>1.088367760636082</v>
+        <v>1.260809002876855</v>
       </c>
       <c r="G19">
-        <v>-6.929128560003274</v>
+        <v>-6.605231405532059</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.504851361696566</v>
       </c>
       <c r="E20">
-        <v>-28.83649584680903</v>
+        <v>-27.83052251684911</v>
       </c>
       <c r="F20">
-        <v>1.181083610561819</v>
+        <v>1.572187339384772</v>
       </c>
       <c r="G20">
-        <v>-7.452396698486017</v>
+        <v>-5.722974329861827</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.131363747110557</v>
       </c>
       <c r="E21">
-        <v>-29.96612368802241</v>
+        <v>-28.64673920046562</v>
       </c>
       <c r="F21">
-        <v>1.213911810734763</v>
+        <v>1.848144685748982</v>
       </c>
       <c r="G21">
-        <v>-7.215457643694839</v>
+        <v>-5.616401247861609</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.823199670222847</v>
       </c>
       <c r="E22">
-        <v>-30.19550448193293</v>
+        <v>-29.56598546046765</v>
       </c>
       <c r="F22">
-        <v>1.562632949760882</v>
+        <v>2.220245666351715</v>
       </c>
       <c r="G22">
-        <v>-7.072352691668764</v>
+        <v>-6.048367850916793</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.582977195501578</v>
       </c>
       <c r="E23">
-        <v>-30.69094218074211</v>
+        <v>-29.75699422987418</v>
       </c>
       <c r="F23">
-        <v>1.484995043300902</v>
+        <v>2.184074175341072</v>
       </c>
       <c r="G23">
-        <v>-6.473431966522595</v>
+        <v>-5.723408011327472</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.403358644015726</v>
       </c>
       <c r="E24">
-        <v>-30.64904021074913</v>
+        <v>-30.11718452397027</v>
       </c>
       <c r="F24">
-        <v>1.926804797584018</v>
+        <v>2.481610492548209</v>
       </c>
       <c r="G24">
-        <v>-6.841147501751603</v>
+        <v>-5.851433428422167</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.271333183852044</v>
       </c>
       <c r="E25">
-        <v>-30.67850699111704</v>
+        <v>-30.8628566394953</v>
       </c>
       <c r="F25">
-        <v>1.936012929633537</v>
+        <v>2.493959793789144</v>
       </c>
       <c r="G25">
-        <v>-6.286770166836328</v>
+        <v>-5.212915268080777</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.165976570702315</v>
       </c>
       <c r="E26">
-        <v>-31.09981809889466</v>
+        <v>-30.56870961032707</v>
       </c>
       <c r="F26">
-        <v>1.713387533396364</v>
+        <v>2.486448158180558</v>
       </c>
       <c r="G26">
-        <v>-7.542734865161649</v>
+        <v>-6.047215781069126</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.071747220644199</v>
       </c>
       <c r="E27">
-        <v>-30.89847082332862</v>
+        <v>-30.83524200499652</v>
       </c>
       <c r="F27">
-        <v>1.805495361648447</v>
+        <v>2.37666462628754</v>
       </c>
       <c r="G27">
-        <v>-7.182279356300263</v>
+        <v>-5.729860264583512</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.9727714262094519</v>
       </c>
       <c r="E28">
-        <v>-31.12107928436068</v>
+        <v>-30.20716756673969</v>
       </c>
       <c r="F28">
-        <v>2.308680513539784</v>
+        <v>2.850250554142045</v>
       </c>
       <c r="G28">
-        <v>-6.468803823858694</v>
+        <v>-5.693325084012115</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.8542636692507591</v>
       </c>
       <c r="E29">
-        <v>-31.6894571140114</v>
+        <v>-30.77086521850348</v>
       </c>
       <c r="F29">
-        <v>2.19970878170151</v>
+        <v>2.514619276814964</v>
       </c>
       <c r="G29">
-        <v>-7.397325773440241</v>
+        <v>-5.882929958682793</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.7115092005351423</v>
       </c>
       <c r="E30">
-        <v>-30.6046204092079</v>
+        <v>-30.75953497653629</v>
       </c>
       <c r="F30">
-        <v>1.715067462489242</v>
+        <v>2.737125388146133</v>
       </c>
       <c r="G30">
-        <v>-7.769050379317306</v>
+        <v>-6.573791154545601</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.5393568118572605</v>
       </c>
       <c r="E31">
-        <v>-30.94463635159982</v>
+        <v>-29.82050154935775</v>
       </c>
       <c r="F31">
-        <v>1.747973529198049</v>
+        <v>2.660423536851316</v>
       </c>
       <c r="G31">
-        <v>-7.961396385694502</v>
+        <v>-6.827743102863094</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.338609276012886</v>
       </c>
       <c r="E32">
-        <v>-30.55430000603466</v>
+        <v>-29.61410728951016</v>
       </c>
       <c r="F32">
-        <v>1.466923380041428</v>
+        <v>2.539024637236243</v>
       </c>
       <c r="G32">
-        <v>-7.903991526043539</v>
+        <v>-6.915197784374021</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.1160829452245793</v>
       </c>
       <c r="E33">
-        <v>-30.44284746799488</v>
+        <v>-30.10542634120936</v>
       </c>
       <c r="F33">
-        <v>1.660878980467709</v>
+        <v>2.467350976076419</v>
       </c>
       <c r="G33">
-        <v>-7.538844974153005</v>
+        <v>-6.958522893846463</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1225603927889264</v>
       </c>
       <c r="E34">
-        <v>-29.23655935454266</v>
+        <v>-30.03190882993183</v>
       </c>
       <c r="F34">
-        <v>1.91401977508921</v>
+        <v>2.420326215354296</v>
       </c>
       <c r="G34">
-        <v>-8.363505178530998</v>
+        <v>-6.661821870980361</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.3664982778224262</v>
       </c>
       <c r="E35">
-        <v>-28.31703912186317</v>
+        <v>-28.57503081455416</v>
       </c>
       <c r="F35">
-        <v>1.99070174556636</v>
+        <v>2.513431397959349</v>
       </c>
       <c r="G35">
-        <v>-8.711758016534631</v>
+        <v>-6.492321939369677</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6052613333451116</v>
       </c>
       <c r="E36">
-        <v>-28.09943236037259</v>
+        <v>-28.85727248555623</v>
       </c>
       <c r="F36">
-        <v>1.705344085915181</v>
+        <v>2.439381979088296</v>
       </c>
       <c r="G36">
-        <v>-8.703200256315615</v>
+        <v>-7.196898725401685</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.8307911982963014</v>
       </c>
       <c r="E37">
-        <v>-28.25140794807001</v>
+        <v>-27.33745773841995</v>
       </c>
       <c r="F37">
-        <v>2.012182969055758</v>
+        <v>2.346629680996835</v>
       </c>
       <c r="G37">
-        <v>-8.396852303748076</v>
+        <v>-7.867016042915419</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.032952735909778</v>
       </c>
       <c r="E38">
-        <v>-27.39200773631635</v>
+        <v>-27.64742725577098</v>
       </c>
       <c r="F38">
-        <v>2.053738848184597</v>
+        <v>2.101706291011106</v>
       </c>
       <c r="G38">
-        <v>-8.605118723623626</v>
+        <v>-6.991025829951028</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.207419190875617</v>
       </c>
       <c r="E39">
-        <v>-27.12864527345227</v>
+        <v>-26.76019504276618</v>
       </c>
       <c r="F39">
-        <v>1.282384660250171</v>
+        <v>2.280759561861024</v>
       </c>
       <c r="G39">
-        <v>-8.210912202989372</v>
+        <v>-6.836175062351618</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.352169334038634</v>
       </c>
       <c r="E40">
-        <v>-26.29436903549317</v>
+        <v>-26.26881485666788</v>
       </c>
       <c r="F40">
-        <v>1.599362760401013</v>
+        <v>1.901889162842614</v>
       </c>
       <c r="G40">
-        <v>-9.695043010426801</v>
+        <v>-7.311132409779776</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.46576425790888</v>
       </c>
       <c r="E41">
-        <v>-25.79650407461588</v>
+        <v>-26.71678056245465</v>
       </c>
       <c r="F41">
-        <v>1.690963627802582</v>
+        <v>2.384452936608661</v>
       </c>
       <c r="G41">
-        <v>-8.668962594348471</v>
+        <v>-6.443080885018557</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.553056276110823</v>
       </c>
       <c r="E42">
-        <v>-25.62857014451543</v>
+        <v>-24.66480219230699</v>
       </c>
       <c r="F42">
-        <v>1.737102035403709</v>
+        <v>2.170788818934973</v>
       </c>
       <c r="G42">
-        <v>-8.760621668694274</v>
+        <v>-7.982060810950633</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.618434621486096</v>
       </c>
       <c r="E43">
-        <v>-25.09843074938548</v>
+        <v>-24.57474895819046</v>
       </c>
       <c r="F43">
-        <v>1.764895418502438</v>
+        <v>2.372497938251458</v>
       </c>
       <c r="G43">
-        <v>-9.898336990902367</v>
+        <v>-6.532763563677413</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.668229933209018</v>
       </c>
       <c r="E44">
-        <v>-24.55417610077361</v>
+        <v>-24.58608825710567</v>
       </c>
       <c r="F44">
-        <v>1.570396409059919</v>
+        <v>2.32656330903142</v>
       </c>
       <c r="G44">
-        <v>-9.283462746802449</v>
+        <v>-7.07586518048593</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.711251715950291</v>
       </c>
       <c r="E45">
-        <v>-24.31545759345927</v>
+        <v>-24.59191187467953</v>
       </c>
       <c r="F45">
-        <v>1.518210919418356</v>
+        <v>2.227087981098839</v>
       </c>
       <c r="G45">
-        <v>-8.803006583233563</v>
+        <v>-7.001659302223167</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.753197697063281</v>
       </c>
       <c r="E46">
-        <v>-23.36328253471047</v>
+        <v>-24.06312196480387</v>
       </c>
       <c r="F46">
-        <v>2.036694360504595</v>
+        <v>2.24497243332528</v>
       </c>
       <c r="G46">
-        <v>-8.841382427124794</v>
+        <v>-7.250784475144402</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.800751986091572</v>
       </c>
       <c r="E47">
-        <v>-22.98387339692583</v>
+        <v>-23.41592604504964</v>
       </c>
       <c r="F47">
-        <v>1.340761367860257</v>
+        <v>2.447963865381299</v>
       </c>
       <c r="G47">
-        <v>-9.347439039348865</v>
+        <v>-8.103590937697277</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.858684364421288</v>
       </c>
       <c r="E48">
-        <v>-22.44099540441229</v>
+        <v>-22.27850922854308</v>
       </c>
       <c r="F48">
-        <v>1.369000412621692</v>
+        <v>2.13695498073503</v>
       </c>
       <c r="G48">
-        <v>-9.177846412463081</v>
+        <v>-7.12750969089856</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.927380969339843</v>
       </c>
       <c r="E49">
-        <v>-22.21209010027258</v>
+        <v>-22.32201427833477</v>
       </c>
       <c r="F49">
-        <v>1.823104795897159</v>
+        <v>1.886711815288522</v>
       </c>
       <c r="G49">
-        <v>-8.950077568815685</v>
+        <v>-7.100191069108495</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.008906146961516</v>
       </c>
       <c r="E50">
-        <v>-21.0515825948009</v>
+        <v>-22.04224062566688</v>
       </c>
       <c r="F50">
-        <v>1.59120996842266</v>
+        <v>1.912146008024078</v>
       </c>
       <c r="G50">
-        <v>-9.423902709669413</v>
+        <v>-7.166084167522149</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.102964987646052</v>
       </c>
       <c r="E51">
-        <v>-21.82554861592585</v>
+        <v>-20.07547907939557</v>
       </c>
       <c r="F51">
-        <v>1.139307385703834</v>
+        <v>2.170043288272454</v>
       </c>
       <c r="G51">
-        <v>-9.975893141250872</v>
+        <v>-6.970000555231116</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.207446207417478</v>
       </c>
       <c r="E52">
-        <v>-20.52866158723917</v>
+        <v>-20.44137072226732</v>
       </c>
       <c r="F52">
-        <v>1.25992596322547</v>
+        <v>1.881718416584446</v>
       </c>
       <c r="G52">
-        <v>-9.329135033062235</v>
+        <v>-7.036429962022132</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.322308051862129</v>
       </c>
       <c r="E53">
-        <v>-20.10420771850023</v>
+        <v>-20.11795616558752</v>
       </c>
       <c r="F53">
-        <v>1.609097734118712</v>
+        <v>2.022764534259118</v>
       </c>
       <c r="G53">
-        <v>-9.22804421447505</v>
+        <v>-7.244107104791692</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.444783695000624</v>
       </c>
       <c r="E54">
-        <v>-19.38362787745171</v>
+        <v>-19.88837611882065</v>
       </c>
       <c r="F54">
-        <v>1.156002302339856</v>
+        <v>2.284848383361243</v>
       </c>
       <c r="G54">
-        <v>-8.508209124052541</v>
+        <v>-7.717832929279242</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.574230775531255</v>
       </c>
       <c r="E55">
-        <v>-20.06025887825579</v>
+        <v>-18.45362875591847</v>
       </c>
       <c r="F55">
-        <v>1.017018819498154</v>
+        <v>1.275997947574586</v>
       </c>
       <c r="G55">
-        <v>-9.350044438688272</v>
+        <v>-7.243309263316728</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.710748188790257</v>
       </c>
       <c r="E56">
-        <v>-19.02818795258966</v>
+        <v>-18.69262802862129</v>
       </c>
       <c r="F56">
-        <v>0.8693010307613355</v>
+        <v>1.430423855539276</v>
       </c>
       <c r="G56">
-        <v>-9.372410484351589</v>
+        <v>-7.317243676845271</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.850818930969361</v>
       </c>
       <c r="E57">
-        <v>-18.35445064667648</v>
+        <v>-17.79520674909923</v>
       </c>
       <c r="F57">
-        <v>0.927616439183615</v>
+        <v>1.81664850035974</v>
       </c>
       <c r="G57">
-        <v>-9.392134714674565</v>
+        <v>-7.718461932931703</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.99446553961132</v>
       </c>
       <c r="E58">
-        <v>-17.89255988331613</v>
+        <v>-17.81669435826563</v>
       </c>
       <c r="F58">
-        <v>0.7958198719286025</v>
+        <v>1.311377519348153</v>
       </c>
       <c r="G58">
-        <v>-9.864248303484491</v>
+        <v>-7.794376052692731</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.14019509814133</v>
       </c>
       <c r="E59">
-        <v>-17.79938653060831</v>
+        <v>-17.28867428897126</v>
       </c>
       <c r="F59">
-        <v>0.8065588269384952</v>
+        <v>1.196380243021915</v>
       </c>
       <c r="G59">
-        <v>-9.764961732216209</v>
+        <v>-8.088246559122755</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.284927542203429</v>
       </c>
       <c r="E60">
-        <v>-17.09334309112441</v>
+        <v>-17.28246122263274</v>
       </c>
       <c r="F60">
-        <v>1.037772736407893</v>
+        <v>1.456230813606092</v>
       </c>
       <c r="G60">
-        <v>-9.645553665160236</v>
+        <v>-8.490345420322633</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.428202837595063</v>
       </c>
       <c r="E61">
-        <v>-17.50574669052894</v>
+        <v>-17.07805043440051</v>
       </c>
       <c r="F61">
-        <v>0.7173420009221829</v>
+        <v>1.301614381138758</v>
       </c>
       <c r="G61">
-        <v>-8.653624836865028</v>
+        <v>-7.52415277304972</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.565875533266056</v>
       </c>
       <c r="E62">
-        <v>-17.14476844195551</v>
+        <v>-16.02569194518001</v>
       </c>
       <c r="F62">
-        <v>0.6663568156472761</v>
+        <v>1.198156262733517</v>
       </c>
       <c r="G62">
-        <v>-9.737755668974478</v>
+        <v>-8.371904032564128</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.696916664173752</v>
       </c>
       <c r="E63">
-        <v>-15.56029161446372</v>
+        <v>-16.93297171261677</v>
       </c>
       <c r="F63">
-        <v>0.8069349057393662</v>
+        <v>1.412781286594452</v>
       </c>
       <c r="G63">
-        <v>-9.903008170658278</v>
+        <v>-8.92243451356277</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.821338719090944</v>
       </c>
       <c r="E64">
-        <v>-15.39824017209923</v>
+        <v>-15.12336179983364</v>
       </c>
       <c r="F64">
-        <v>1.052136627172437</v>
+        <v>1.020872384655978</v>
       </c>
       <c r="G64">
-        <v>-9.869574971257178</v>
+        <v>-8.632861095242719</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.936538045659313</v>
       </c>
       <c r="E65">
-        <v>-16.36841138655452</v>
+        <v>-15.68803080927208</v>
       </c>
       <c r="F65">
-        <v>0.3520137522047393</v>
+        <v>1.346589760906355</v>
       </c>
       <c r="G65">
-        <v>-10.72780079685784</v>
+        <v>-8.153096835691539</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.044038046837976</v>
       </c>
       <c r="E66">
-        <v>-16.00479303763462</v>
+        <v>-15.2425331218195</v>
       </c>
       <c r="F66">
-        <v>0.5789723383259563</v>
+        <v>0.8990145694997537</v>
       </c>
       <c r="G66">
-        <v>-10.64571913075715</v>
+        <v>-8.827266260945342</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.144648451615936</v>
       </c>
       <c r="E67">
-        <v>-16.11168313811167</v>
+        <v>-16.41136849099128</v>
       </c>
       <c r="F67">
-        <v>0.7746998166268263</v>
+        <v>1.091465854722552</v>
       </c>
       <c r="G67">
-        <v>-10.62495869968038</v>
+        <v>-10.0212906522309</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.236830469277824</v>
       </c>
       <c r="E68">
-        <v>-15.41333810444081</v>
+        <v>-14.90342740270312</v>
       </c>
       <c r="F68">
-        <v>0.3002573568778262</v>
+        <v>0.6105140839223531</v>
       </c>
       <c r="G68">
-        <v>-11.01694384425779</v>
+        <v>-8.832844530179013</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.320658037917169</v>
       </c>
       <c r="E69">
-        <v>-15.95260237469622</v>
+        <v>-15.31443170363928</v>
       </c>
       <c r="F69">
-        <v>0.5413967645675679</v>
+        <v>1.083460512141897</v>
       </c>
       <c r="G69">
-        <v>-9.576763839399721</v>
+        <v>-9.075941199673236</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.392660132103124</v>
       </c>
       <c r="E70">
-        <v>-15.92063134820206</v>
+        <v>-15.61012747091813</v>
       </c>
       <c r="F70">
-        <v>0.7776421776415702</v>
+        <v>0.7544810250592959</v>
       </c>
       <c r="G70">
-        <v>-9.597580549750658</v>
+        <v>-9.391816902302796</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.450109419162533</v>
       </c>
       <c r="E71">
-        <v>-15.99100836275527</v>
+        <v>-16.05730069375355</v>
       </c>
       <c r="F71">
-        <v>0.5327179592884375</v>
+        <v>0.5227054824907998</v>
       </c>
       <c r="G71">
-        <v>-10.45407827057982</v>
+        <v>-9.256657259570972</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.491343498543477</v>
       </c>
       <c r="E72">
-        <v>-16.19462666803616</v>
+        <v>-16.5743890267934</v>
       </c>
       <c r="F72">
-        <v>0.3442494645382996</v>
+        <v>0.8285271304607381</v>
       </c>
       <c r="G72">
-        <v>-9.719954865609816</v>
+        <v>-8.934792780060869</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.512344367227403</v>
       </c>
       <c r="E73">
-        <v>-15.67216303634921</v>
+        <v>-15.38383962475484</v>
       </c>
       <c r="F73">
-        <v>0.5069143146912329</v>
+        <v>0.6209987301395864</v>
       </c>
       <c r="G73">
-        <v>-9.924827976307615</v>
+        <v>-8.95809239956626</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.51056802478924</v>
       </c>
       <c r="E74">
-        <v>-15.67631564701424</v>
+        <v>-15.99577231741134</v>
       </c>
       <c r="F74">
-        <v>0.4233676635470832</v>
+        <v>0.5639117905756585</v>
       </c>
       <c r="G74">
-        <v>-10.26953190949315</v>
+        <v>-8.935845533542357</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.485672617529146</v>
       </c>
       <c r="E75">
-        <v>-15.49532159787567</v>
+        <v>-16.48574414809325</v>
       </c>
       <c r="F75">
-        <v>0.5673627691757213</v>
+        <v>0.337451053263524</v>
       </c>
       <c r="G75">
-        <v>-9.259352043639938</v>
+        <v>-8.976538759311079</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.434234640803352</v>
       </c>
       <c r="E76">
-        <v>-16.68246105898645</v>
+        <v>-16.32809438246423</v>
       </c>
       <c r="F76">
-        <v>0.09881000166062567</v>
+        <v>0.3516906889176475</v>
       </c>
       <c r="G76">
-        <v>-9.114449465386038</v>
+        <v>-9.347263580435284</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.354158612609326</v>
       </c>
       <c r="E77">
-        <v>-16.77846923642307</v>
+        <v>-17.25814784568556</v>
       </c>
       <c r="F77">
-        <v>0.5079737965994134</v>
+        <v>0.6285907173862439</v>
       </c>
       <c r="G77">
-        <v>-9.050469862294083</v>
+        <v>-9.318415486606074</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.244082101761001</v>
       </c>
       <c r="E78">
-        <v>-17.70671131004134</v>
+        <v>-16.77728730470707</v>
       </c>
       <c r="F78">
-        <v>0.2298452992724655</v>
+        <v>0.5304855091378928</v>
       </c>
       <c r="G78">
-        <v>-8.030921152564735</v>
+        <v>-8.781531074320309</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.099977240747498</v>
       </c>
       <c r="E79">
-        <v>-17.88446750026442</v>
+        <v>-18.65554888344648</v>
       </c>
       <c r="F79">
-        <v>-0.1436605924454148</v>
+        <v>0.5288312594345023</v>
       </c>
       <c r="G79">
-        <v>-8.493351395672292</v>
+        <v>-8.509923986641883</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.920684571966112</v>
       </c>
       <c r="E80">
-        <v>-18.82637650843783</v>
+        <v>-18.77525456536524</v>
       </c>
       <c r="F80">
-        <v>0.01354200305345857</v>
+        <v>0.2760996783099843</v>
       </c>
       <c r="G80">
-        <v>-8.446351580651259</v>
+        <v>-7.731478997992117</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.704471324036439</v>
       </c>
       <c r="E81">
-        <v>-18.33989160274182</v>
+        <v>-19.63869870440775</v>
       </c>
       <c r="F81">
-        <v>0.09604656800488652</v>
+        <v>0.255740064283978</v>
       </c>
       <c r="G81">
-        <v>-8.270154415414629</v>
+        <v>-7.20677739329087</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.446995848402282</v>
       </c>
       <c r="E82">
-        <v>-21.60303751708496</v>
+        <v>-20.37306322033562</v>
       </c>
       <c r="F82">
-        <v>0.04815367824463031</v>
+        <v>0.1722953023303726</v>
       </c>
       <c r="G82">
-        <v>-7.570540137145988</v>
+        <v>-7.314164869493749</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.151451474172957</v>
       </c>
       <c r="E83">
-        <v>-21.41452167261965</v>
+        <v>-20.53938048521533</v>
       </c>
       <c r="F83">
-        <v>-0.08323036204378807</v>
+        <v>0.3180167256264448</v>
       </c>
       <c r="G83">
-        <v>-7.529684694645843</v>
+        <v>-7.553514001437517</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.817804151391439</v>
       </c>
       <c r="E84">
-        <v>-22.26720162894592</v>
+        <v>-22.04450486267072</v>
       </c>
       <c r="F84">
-        <v>0.3175553249830855</v>
+        <v>-0.04172667006132445</v>
       </c>
       <c r="G84">
-        <v>-6.832702300080922</v>
+        <v>-6.417887633464703</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.448599581265008</v>
       </c>
       <c r="E85">
-        <v>-23.44397088457914</v>
+        <v>-22.90068080093091</v>
       </c>
       <c r="F85">
-        <v>-0.03625033316141692</v>
+        <v>0.1666731727675724</v>
       </c>
       <c r="G85">
-        <v>-6.9517230333088</v>
+        <v>-7.316257134274569</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.053261283332528</v>
       </c>
       <c r="E86">
-        <v>-24.186595337097</v>
+        <v>-24.63688867852371</v>
       </c>
       <c r="F86">
-        <v>0.0813546437488345</v>
+        <v>0.2611865799573848</v>
       </c>
       <c r="G86">
-        <v>-7.107464337658274</v>
+        <v>-5.935441832026713</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.637792408114756</v>
       </c>
       <c r="E87">
-        <v>-25.72674293252772</v>
+        <v>-25.26963423771946</v>
       </c>
       <c r="F87">
-        <v>-0.3960434308933542</v>
+        <v>0.06047978519828695</v>
       </c>
       <c r="G87">
-        <v>-6.59782571516071</v>
+        <v>-5.981160465924049</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.215618276373712</v>
       </c>
       <c r="E88">
-        <v>-26.95864635920432</v>
+        <v>-26.75312609484021</v>
       </c>
       <c r="F88">
-        <v>-0.3243937923882109</v>
+        <v>0.02522281180033439</v>
       </c>
       <c r="G88">
-        <v>-6.186308351901605</v>
+        <v>-5.919643908713311</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8009849287542337</v>
       </c>
       <c r="E89">
-        <v>-27.84734579778761</v>
+        <v>-28.64451571972786</v>
       </c>
       <c r="F89">
-        <v>-0.2913783811822339</v>
+        <v>-0.1098168138366382</v>
       </c>
       <c r="G89">
-        <v>-5.631083517328277</v>
+        <v>-6.529936357786876</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.4059513252423386</v>
       </c>
       <c r="E90">
-        <v>-28.90108094310643</v>
+        <v>-30.09581239089107</v>
       </c>
       <c r="F90">
-        <v>-0.443607458794699</v>
+        <v>-0.01604976567674817</v>
       </c>
       <c r="G90">
-        <v>-5.787513415149919</v>
+        <v>-5.935693433487698</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.04927555335823367</v>
       </c>
       <c r="E91">
-        <v>-31.1568723429173</v>
+        <v>-31.98094366470012</v>
       </c>
       <c r="F91">
-        <v>-0.5538424509222432</v>
+        <v>-0.2276222556583671</v>
       </c>
       <c r="G91">
-        <v>-6.456041670804804</v>
+        <v>-6.351617132859572</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.2548788119847189</v>
       </c>
       <c r="E92">
-        <v>-32.81602823526959</v>
+        <v>-33.75168342083841</v>
       </c>
       <c r="F92">
-        <v>-0.5974916144779575</v>
+        <v>-0.1908303174630271</v>
       </c>
       <c r="G92">
-        <v>-6.779101257254583</v>
+        <v>-6.282416799452187</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.4909530372029943</v>
       </c>
       <c r="E93">
-        <v>-34.94158751533087</v>
+        <v>-35.07510730721003</v>
       </c>
       <c r="F93">
-        <v>-0.7388417429894568</v>
+        <v>-0.2313697897886321</v>
       </c>
       <c r="G93">
-        <v>-6.944929793862215</v>
+        <v>-5.843441771490367</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.6443768964003347</v>
       </c>
       <c r="E94">
-        <v>-37.01068578146453</v>
+        <v>-37.46192557395884</v>
       </c>
       <c r="F94">
-        <v>-0.8022855740024681</v>
+        <v>-0.421499161181383</v>
       </c>
       <c r="G94">
-        <v>-6.02194307642233</v>
+        <v>-5.939103295393148</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.7068231113439873</v>
       </c>
       <c r="E95">
-        <v>-38.59727740631791</v>
+        <v>-39.91779627661361</v>
       </c>
       <c r="F95">
-        <v>-1.031838606829253</v>
+        <v>-0.3849532481046744</v>
       </c>
       <c r="G95">
-        <v>-6.531684325831611</v>
+        <v>-5.599653197978436</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.6642695365364155</v>
       </c>
       <c r="E96">
-        <v>-42.11553037540914</v>
+        <v>-41.41342897254892</v>
       </c>
       <c r="F96">
-        <v>-1.245670054718306</v>
+        <v>-0.143358238343393</v>
       </c>
       <c r="G96">
-        <v>-6.991214531046766</v>
+        <v>-6.588096021820792</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.5225179916943945</v>
       </c>
       <c r="E97">
-        <v>-43.18490234147645</v>
+        <v>-44.03462067580171</v>
       </c>
       <c r="F97">
-        <v>-1.529110043832005</v>
+        <v>-0.57134088393898</v>
       </c>
       <c r="G97">
-        <v>-6.267621971437184</v>
+        <v>-7.22258524824089</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.2663314541377596</v>
       </c>
       <c r="E98">
-        <v>-45.67981754702536</v>
+        <v>-46.17601602946782</v>
       </c>
       <c r="F98">
-        <v>-1.520984587977944</v>
+        <v>-0.5456316732256945</v>
       </c>
       <c r="G98">
-        <v>-6.81890394627324</v>
+        <v>-7.214871677134388</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.07646421981092609</v>
       </c>
       <c r="E99">
-        <v>-48.3886488077486</v>
+        <v>-48.80502387885785</v>
       </c>
       <c r="F99">
-        <v>-1.920377789400712</v>
+        <v>-0.8547974404007344</v>
       </c>
       <c r="G99">
-        <v>-7.395869133402962</v>
+        <v>-7.824485464372402</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.5361467686954116</v>
       </c>
       <c r="E100">
-        <v>-50.11087502184271</v>
+        <v>-51.22523737717622</v>
       </c>
       <c r="F100">
-        <v>-2.082702180551095</v>
+        <v>-1.346535383152785</v>
       </c>
       <c r="G100">
-        <v>-7.513936429515529</v>
+        <v>-7.369434427271881</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.041961658812006</v>
       </c>
       <c r="E101">
-        <v>-52.75190710184161</v>
+        <v>-53.31915734146442</v>
       </c>
       <c r="F101">
-        <v>-2.354400890097513</v>
+        <v>-1.124148556727619</v>
       </c>
       <c r="G101">
-        <v>-8.003195333673339</v>
+        <v>-8.71266841655793</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.684005035984897</v>
       </c>
       <c r="E102">
-        <v>-54.80146726686917</v>
+        <v>-56.18744409682724</v>
       </c>
       <c r="F102">
-        <v>-2.561838170004357</v>
+        <v>-1.194324529623182</v>
       </c>
       <c r="G102">
-        <v>-8.065410415992863</v>
+        <v>-8.894778216127699</v>
       </c>
     </row>
   </sheetData>
